--- a/artfynd/A 23822-2024 artfynd.xlsx
+++ b/artfynd/A 23822-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124800244</v>
+        <v>124800234</v>
       </c>
       <c r="B2" t="n">
-        <v>91008</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442759</v>
+        <v>442904</v>
       </c>
       <c r="R2" t="n">
-        <v>7000122</v>
+        <v>7000228</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800242</v>
+        <v>124800250</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -819,24 +819,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442778</v>
+        <v>442699</v>
       </c>
       <c r="R3" t="n">
-        <v>7000153</v>
+        <v>7000206</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800247</v>
+        <v>124800236</v>
       </c>
       <c r="B4" t="n">
-        <v>74906</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1467</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442741</v>
+        <v>442848</v>
       </c>
       <c r="R4" t="n">
-        <v>7000167</v>
+        <v>7000225</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800238</v>
+        <v>124800247</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>74906</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1039,24 +1031,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442812</v>
+        <v>442741</v>
       </c>
       <c r="R5" t="n">
-        <v>7000185</v>
+        <v>7000167</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800237</v>
+        <v>124800252</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1159,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>442847</v>
+        <v>442674</v>
       </c>
       <c r="R6" t="n">
-        <v>7000224</v>
+        <v>7000139</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800236</v>
+        <v>124800235</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1265,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>442848</v>
+        <v>442902</v>
       </c>
       <c r="R7" t="n">
-        <v>7000225</v>
+        <v>7000213</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800249</v>
+        <v>124800244</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1371,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442738</v>
+        <v>442759</v>
       </c>
       <c r="R8" t="n">
-        <v>7000132</v>
+        <v>7000122</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800248</v>
+        <v>124800245</v>
       </c>
       <c r="B9" t="n">
-        <v>91299</v>
+        <v>91008</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1477,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442739</v>
+        <v>442754</v>
       </c>
       <c r="R9" t="n">
-        <v>7000176</v>
+        <v>7000189</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800251</v>
+        <v>124800242</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1555,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1577,16 +1561,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442674</v>
+        <v>442778</v>
       </c>
       <c r="R10" t="n">
-        <v>7000138</v>
+        <v>7000153</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1645,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800245</v>
+        <v>124800240</v>
       </c>
       <c r="B11" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1661,21 +1653,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1683,16 +1675,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442754</v>
+        <v>442790</v>
       </c>
       <c r="R11" t="n">
-        <v>7000189</v>
+        <v>7000196</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800235</v>
+        <v>124800237</v>
       </c>
       <c r="B12" t="n">
-        <v>91008</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1767,21 +1767,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442902</v>
+        <v>442847</v>
       </c>
       <c r="R12" t="n">
-        <v>7000213</v>
+        <v>7000224</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800252</v>
+        <v>124800249</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442674</v>
+        <v>442738</v>
       </c>
       <c r="R13" t="n">
-        <v>7000139</v>
+        <v>7000132</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2069,10 +2069,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800246</v>
+        <v>124800239</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>74906</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,21 +2085,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442748</v>
+        <v>442803</v>
       </c>
       <c r="R15" t="n">
-        <v>7000187</v>
+        <v>7000212</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800234</v>
+        <v>124800248</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>442904</v>
+        <v>442739</v>
       </c>
       <c r="R16" t="n">
-        <v>7000228</v>
+        <v>7000176</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2281,10 +2281,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800239</v>
+        <v>124800241</v>
       </c>
       <c r="B17" t="n">
-        <v>74906</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2297,21 +2297,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2319,16 +2319,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442803</v>
+        <v>442785</v>
       </c>
       <c r="R17" t="n">
-        <v>7000212</v>
+        <v>7000194</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800240</v>
+        <v>124800251</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2403,21 +2411,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2425,24 +2433,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442790</v>
+        <v>442674</v>
       </c>
       <c r="R18" t="n">
-        <v>7000196</v>
+        <v>7000138</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2501,10 +2501,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800241</v>
+        <v>124800246</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2517,21 +2517,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2539,24 +2539,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442785</v>
+        <v>442748</v>
       </c>
       <c r="R19" t="n">
-        <v>7000194</v>
+        <v>7000187</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2615,10 +2607,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800250</v>
+        <v>124800238</v>
       </c>
       <c r="B20" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,21 +2623,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2653,16 +2645,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>442699</v>
+        <v>442812</v>
       </c>
       <c r="R20" t="n">
-        <v>7000206</v>
+        <v>7000185</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 23822-2024 artfynd.xlsx
+++ b/artfynd/A 23822-2024 artfynd.xlsx
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800245</v>
+        <v>124800242</v>
       </c>
       <c r="B9" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1455,16 +1455,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442754</v>
+        <v>442778</v>
       </c>
       <c r="R9" t="n">
-        <v>7000189</v>
+        <v>7000153</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800242</v>
+        <v>124800240</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1575,10 +1583,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442778</v>
+        <v>442790</v>
       </c>
       <c r="R10" t="n">
-        <v>7000153</v>
+        <v>7000196</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,10 +1645,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800240</v>
+        <v>124800237</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1653,21 +1661,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1675,24 +1683,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442790</v>
+        <v>442847</v>
       </c>
       <c r="R11" t="n">
-        <v>7000196</v>
+        <v>7000224</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800237</v>
+        <v>124800245</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1767,21 +1767,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442847</v>
+        <v>442754</v>
       </c>
       <c r="R12" t="n">
-        <v>7000224</v>
+        <v>7000189</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 23822-2024 artfynd.xlsx
+++ b/artfynd/A 23822-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124800234</v>
+        <v>124800237</v>
       </c>
       <c r="B2" t="n">
         <v>91012</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442904</v>
+        <v>442847</v>
       </c>
       <c r="R2" t="n">
-        <v>7000228</v>
+        <v>7000224</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800250</v>
+        <v>124800242</v>
       </c>
       <c r="B3" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -819,16 +819,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442699</v>
+        <v>442778</v>
       </c>
       <c r="R3" t="n">
-        <v>7000206</v>
+        <v>7000153</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800236</v>
+        <v>124800246</v>
       </c>
       <c r="B4" t="n">
         <v>91012</v>
@@ -931,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442848</v>
+        <v>442748</v>
       </c>
       <c r="R4" t="n">
-        <v>7000225</v>
+        <v>7000187</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800247</v>
+        <v>124800236</v>
       </c>
       <c r="B5" t="n">
-        <v>74906</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1467</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442741</v>
+        <v>442848</v>
       </c>
       <c r="R5" t="n">
-        <v>7000167</v>
+        <v>7000225</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800252</v>
+        <v>124800250</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>82597</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1123,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>442674</v>
+        <v>442699</v>
       </c>
       <c r="R6" t="n">
-        <v>7000139</v>
+        <v>7000206</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800235</v>
+        <v>124800239</v>
       </c>
       <c r="B7" t="n">
-        <v>91008</v>
+        <v>74906</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1229,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1249,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>442902</v>
+        <v>442803</v>
       </c>
       <c r="R7" t="n">
-        <v>7000213</v>
+        <v>7000212</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800244</v>
+        <v>124800247</v>
       </c>
       <c r="B8" t="n">
-        <v>91008</v>
+        <v>74906</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1335,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1355,10 +1363,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442759</v>
+        <v>442741</v>
       </c>
       <c r="R8" t="n">
-        <v>7000122</v>
+        <v>7000167</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1425,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800242</v>
+        <v>124800244</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1441,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1455,24 +1463,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442778</v>
+        <v>442759</v>
       </c>
       <c r="R9" t="n">
-        <v>7000153</v>
+        <v>7000122</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800240</v>
+        <v>124800235</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1547,21 +1547,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1569,24 +1569,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442790</v>
+        <v>442902</v>
       </c>
       <c r="R10" t="n">
-        <v>7000196</v>
+        <v>7000213</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1645,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800237</v>
+        <v>124800252</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1661,21 +1653,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1689,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442847</v>
+        <v>442674</v>
       </c>
       <c r="R11" t="n">
-        <v>7000224</v>
+        <v>7000139</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1857,10 +1849,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800249</v>
+        <v>124800243</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1869,25 +1861,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1901,10 +1893,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442738</v>
+        <v>442768</v>
       </c>
       <c r="R13" t="n">
-        <v>7000132</v>
+        <v>7000121</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1963,10 +1955,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800243</v>
+        <v>124800241</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1975,25 +1967,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2001,16 +1993,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442768</v>
+        <v>442785</v>
       </c>
       <c r="R14" t="n">
-        <v>7000121</v>
+        <v>7000194</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2069,10 +2069,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800239</v>
+        <v>124800234</v>
       </c>
       <c r="B15" t="n">
-        <v>74906</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,21 +2085,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1467</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442803</v>
+        <v>442904</v>
       </c>
       <c r="R15" t="n">
-        <v>7000212</v>
+        <v>7000228</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800248</v>
+        <v>124800249</v>
       </c>
       <c r="B16" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>442739</v>
+        <v>442738</v>
       </c>
       <c r="R16" t="n">
-        <v>7000176</v>
+        <v>7000132</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2281,7 +2281,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800241</v>
+        <v>124800240</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442785</v>
+        <v>442790</v>
       </c>
       <c r="R17" t="n">
-        <v>7000194</v>
+        <v>7000196</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800251</v>
+        <v>124800238</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2411,21 +2411,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2433,16 +2433,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442674</v>
+        <v>442812</v>
       </c>
       <c r="R18" t="n">
-        <v>7000138</v>
+        <v>7000185</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2501,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800246</v>
+        <v>124800248</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2517,21 +2525,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2545,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442748</v>
+        <v>442739</v>
       </c>
       <c r="R19" t="n">
-        <v>7000187</v>
+        <v>7000176</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2607,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800238</v>
+        <v>124800251</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2623,21 +2631,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2645,24 +2653,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>442812</v>
+        <v>442674</v>
       </c>
       <c r="R20" t="n">
-        <v>7000185</v>
+        <v>7000138</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 23822-2024 artfynd.xlsx
+++ b/artfynd/A 23822-2024 artfynd.xlsx
@@ -2069,10 +2069,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800234</v>
+        <v>124800249</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,21 +2085,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442904</v>
+        <v>442738</v>
       </c>
       <c r="R15" t="n">
-        <v>7000228</v>
+        <v>7000132</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800249</v>
+        <v>124800234</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>442738</v>
+        <v>442904</v>
       </c>
       <c r="R16" t="n">
-        <v>7000132</v>
+        <v>7000228</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 23822-2024 artfynd.xlsx
+++ b/artfynd/A 23822-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124800237</v>
+        <v>124800247</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>74906</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442847</v>
+        <v>442741</v>
       </c>
       <c r="R2" t="n">
-        <v>7000224</v>
+        <v>7000167</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800242</v>
+        <v>124800250</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -819,24 +819,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442778</v>
+        <v>442699</v>
       </c>
       <c r="R3" t="n">
-        <v>7000153</v>
+        <v>7000206</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800246</v>
+        <v>124800242</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -933,16 +925,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442748</v>
+        <v>442778</v>
       </c>
       <c r="R4" t="n">
-        <v>7000187</v>
+        <v>7000153</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800236</v>
+        <v>124800240</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1039,16 +1039,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442848</v>
+        <v>442790</v>
       </c>
       <c r="R5" t="n">
-        <v>7000225</v>
+        <v>7000196</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800250</v>
+        <v>124800238</v>
       </c>
       <c r="B6" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1145,16 +1153,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>442699</v>
+        <v>442812</v>
       </c>
       <c r="R6" t="n">
-        <v>7000206</v>
+        <v>7000185</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800239</v>
+        <v>124800246</v>
       </c>
       <c r="B7" t="n">
-        <v>74906</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,21 +1245,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1467</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1257,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>442803</v>
+        <v>442748</v>
       </c>
       <c r="R7" t="n">
-        <v>7000212</v>
+        <v>7000187</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800247</v>
+        <v>124800244</v>
       </c>
       <c r="B8" t="n">
-        <v>74906</v>
+        <v>91008</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1335,21 +1351,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1363,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442741</v>
+        <v>442759</v>
       </c>
       <c r="R8" t="n">
-        <v>7000167</v>
+        <v>7000122</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,10 +1441,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800244</v>
+        <v>124800237</v>
       </c>
       <c r="B9" t="n">
-        <v>91008</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1441,21 +1457,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1469,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442759</v>
+        <v>442847</v>
       </c>
       <c r="R9" t="n">
-        <v>7000122</v>
+        <v>7000224</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,10 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800235</v>
+        <v>124800249</v>
       </c>
       <c r="B10" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1547,21 +1563,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1575,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442902</v>
+        <v>442738</v>
       </c>
       <c r="R10" t="n">
-        <v>7000213</v>
+        <v>7000132</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800252</v>
+        <v>124800235</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1653,21 +1669,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1681,10 +1697,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442674</v>
+        <v>442902</v>
       </c>
       <c r="R11" t="n">
-        <v>7000139</v>
+        <v>7000213</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800245</v>
+        <v>124800241</v>
       </c>
       <c r="B12" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1759,21 +1775,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1781,16 +1797,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442754</v>
+        <v>442785</v>
       </c>
       <c r="R12" t="n">
-        <v>7000189</v>
+        <v>7000194</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,10 +1873,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800243</v>
+        <v>124800239</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>74906</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1861,25 +1885,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1467</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1893,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442768</v>
+        <v>442803</v>
       </c>
       <c r="R13" t="n">
-        <v>7000121</v>
+        <v>7000212</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1955,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800241</v>
+        <v>124800234</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1971,21 +1995,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1993,24 +2017,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442785</v>
+        <v>442904</v>
       </c>
       <c r="R14" t="n">
-        <v>7000194</v>
+        <v>7000228</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2069,7 +2085,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800249</v>
+        <v>124800251</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2113,10 +2129,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442738</v>
+        <v>442674</v>
       </c>
       <c r="R15" t="n">
-        <v>7000132</v>
+        <v>7000138</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,10 +2191,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800234</v>
+        <v>124800252</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2191,21 +2207,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2219,10 +2235,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>442904</v>
+        <v>442674</v>
       </c>
       <c r="R16" t="n">
-        <v>7000228</v>
+        <v>7000139</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2281,10 +2297,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800240</v>
+        <v>124800248</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2297,21 +2313,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2319,24 +2335,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442790</v>
+        <v>442739</v>
       </c>
       <c r="R17" t="n">
-        <v>7000196</v>
+        <v>7000176</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,10 +2403,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800238</v>
+        <v>124800236</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2411,21 +2419,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2433,24 +2441,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442812</v>
+        <v>442848</v>
       </c>
       <c r="R18" t="n">
-        <v>7000185</v>
+        <v>7000225</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2509,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800248</v>
+        <v>124800243</v>
       </c>
       <c r="B19" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2521,25 +2521,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442739</v>
+        <v>442768</v>
       </c>
       <c r="R19" t="n">
-        <v>7000176</v>
+        <v>7000121</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800251</v>
+        <v>124800245</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,21 +2631,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>442674</v>
+        <v>442754</v>
       </c>
       <c r="R20" t="n">
-        <v>7000138</v>
+        <v>7000189</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 23822-2024 artfynd.xlsx
+++ b/artfynd/A 23822-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124800247</v>
+        <v>124800249</v>
       </c>
       <c r="B2" t="n">
-        <v>74906</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442741</v>
+        <v>442738</v>
       </c>
       <c r="R2" t="n">
-        <v>7000167</v>
+        <v>7000132</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800250</v>
+        <v>124800236</v>
       </c>
       <c r="B3" t="n">
-        <v>82597</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442699</v>
+        <v>442848</v>
       </c>
       <c r="R3" t="n">
-        <v>7000206</v>
+        <v>7000225</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800242</v>
+        <v>124800246</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -925,24 +925,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442778</v>
+        <v>442748</v>
       </c>
       <c r="R4" t="n">
-        <v>7000153</v>
+        <v>7000187</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800240</v>
+        <v>124800248</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1039,24 +1031,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442790</v>
+        <v>442739</v>
       </c>
       <c r="R5" t="n">
-        <v>7000196</v>
+        <v>7000176</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800238</v>
+        <v>124800247</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>74906</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1153,24 +1137,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>442812</v>
+        <v>442741</v>
       </c>
       <c r="R6" t="n">
-        <v>7000185</v>
+        <v>7000167</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800246</v>
+        <v>124800235</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1273,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>442748</v>
+        <v>442902</v>
       </c>
       <c r="R7" t="n">
-        <v>7000187</v>
+        <v>7000213</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800244</v>
+        <v>124800240</v>
       </c>
       <c r="B8" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1351,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1373,16 +1349,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442759</v>
+        <v>442790</v>
       </c>
       <c r="R8" t="n">
-        <v>7000122</v>
+        <v>7000196</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,10 +1425,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800237</v>
+        <v>124800251</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1457,21 +1441,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1485,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442847</v>
+        <v>442674</v>
       </c>
       <c r="R9" t="n">
-        <v>7000224</v>
+        <v>7000138</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800249</v>
+        <v>124800252</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1591,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442738</v>
+        <v>442674</v>
       </c>
       <c r="R10" t="n">
-        <v>7000132</v>
+        <v>7000139</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800235</v>
+        <v>124800242</v>
       </c>
       <c r="B11" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,21 +1653,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1691,16 +1675,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442902</v>
+        <v>442778</v>
       </c>
       <c r="R11" t="n">
-        <v>7000213</v>
+        <v>7000153</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1759,7 +1751,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800241</v>
+        <v>124800238</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1811,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442785</v>
+        <v>442812</v>
       </c>
       <c r="R12" t="n">
-        <v>7000194</v>
+        <v>7000185</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,10 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800239</v>
+        <v>124800245</v>
       </c>
       <c r="B13" t="n">
-        <v>74906</v>
+        <v>91008</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1889,21 +1881,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1917,10 +1909,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442803</v>
+        <v>442754</v>
       </c>
       <c r="R13" t="n">
-        <v>7000212</v>
+        <v>7000189</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800234</v>
+        <v>124800244</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1995,21 +1987,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2023,10 +2015,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442904</v>
+        <v>442759</v>
       </c>
       <c r="R14" t="n">
-        <v>7000228</v>
+        <v>7000122</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2085,10 +2077,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800251</v>
+        <v>124800239</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>74906</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2101,21 +2093,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2129,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442674</v>
+        <v>442803</v>
       </c>
       <c r="R15" t="n">
-        <v>7000138</v>
+        <v>7000212</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2191,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800252</v>
+        <v>124800243</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2203,25 +2195,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2235,10 +2227,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>442674</v>
+        <v>442768</v>
       </c>
       <c r="R16" t="n">
-        <v>7000139</v>
+        <v>7000121</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2297,10 +2289,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800248</v>
+        <v>124800234</v>
       </c>
       <c r="B17" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2313,21 +2305,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2341,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442739</v>
+        <v>442904</v>
       </c>
       <c r="R17" t="n">
-        <v>7000176</v>
+        <v>7000228</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2403,7 +2395,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800236</v>
+        <v>124800237</v>
       </c>
       <c r="B18" t="n">
         <v>91012</v>
@@ -2447,10 +2439,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442848</v>
+        <v>442847</v>
       </c>
       <c r="R18" t="n">
-        <v>7000225</v>
+        <v>7000224</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2509,10 +2501,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800243</v>
+        <v>124800241</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2521,25 +2513,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2547,16 +2539,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442768</v>
+        <v>442785</v>
       </c>
       <c r="R19" t="n">
-        <v>7000121</v>
+        <v>7000194</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800245</v>
+        <v>124800250</v>
       </c>
       <c r="B20" t="n">
-        <v>91008</v>
+        <v>82597</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,21 +2631,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>442754</v>
+        <v>442699</v>
       </c>
       <c r="R20" t="n">
-        <v>7000189</v>
+        <v>7000206</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 23822-2024 artfynd.xlsx
+++ b/artfynd/A 23822-2024 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800246</v>
+        <v>124800248</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442748</v>
+        <v>442739</v>
       </c>
       <c r="R4" t="n">
-        <v>7000187</v>
+        <v>7000176</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800248</v>
+        <v>124800246</v>
       </c>
       <c r="B5" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442739</v>
+        <v>442748</v>
       </c>
       <c r="R5" t="n">
-        <v>7000176</v>
+        <v>7000187</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1971,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800244</v>
+        <v>124800239</v>
       </c>
       <c r="B14" t="n">
-        <v>91008</v>
+        <v>74906</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1987,21 +1987,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442759</v>
+        <v>442803</v>
       </c>
       <c r="R14" t="n">
-        <v>7000122</v>
+        <v>7000212</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,10 +2077,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800239</v>
+        <v>124800244</v>
       </c>
       <c r="B15" t="n">
-        <v>74906</v>
+        <v>91008</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2093,21 +2093,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442803</v>
+        <v>442759</v>
       </c>
       <c r="R15" t="n">
-        <v>7000212</v>
+        <v>7000122</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800243</v>
+        <v>124800237</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2195,25 +2195,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2227,10 +2227,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>442768</v>
+        <v>442847</v>
       </c>
       <c r="R16" t="n">
-        <v>7000121</v>
+        <v>7000224</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2289,10 +2289,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800234</v>
+        <v>124800243</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2301,25 +2301,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442904</v>
+        <v>442768</v>
       </c>
       <c r="R17" t="n">
-        <v>7000228</v>
+        <v>7000121</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,7 +2395,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800237</v>
+        <v>124800234</v>
       </c>
       <c r="B18" t="n">
         <v>91012</v>
@@ -2439,10 +2439,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442847</v>
+        <v>442904</v>
       </c>
       <c r="R18" t="n">
-        <v>7000224</v>
+        <v>7000228</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 23822-2024 artfynd.xlsx
+++ b/artfynd/A 23822-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124800249</v>
+        <v>124800241</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,16 +713,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442738</v>
+        <v>442785</v>
       </c>
       <c r="R2" t="n">
-        <v>7000132</v>
+        <v>7000194</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800236</v>
+        <v>124800252</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +805,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442848</v>
+        <v>442674</v>
       </c>
       <c r="R3" t="n">
-        <v>7000225</v>
+        <v>7000139</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800248</v>
+        <v>124800239</v>
       </c>
       <c r="B4" t="n">
-        <v>91299</v>
+        <v>74906</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1467</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442739</v>
+        <v>442803</v>
       </c>
       <c r="R4" t="n">
-        <v>7000176</v>
+        <v>7000212</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800246</v>
+        <v>124800235</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442748</v>
+        <v>442902</v>
       </c>
       <c r="R5" t="n">
-        <v>7000187</v>
+        <v>7000213</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800247</v>
+        <v>124800245</v>
       </c>
       <c r="B6" t="n">
-        <v>74906</v>
+        <v>91008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1123,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>442741</v>
+        <v>442754</v>
       </c>
       <c r="R6" t="n">
-        <v>7000167</v>
+        <v>7000189</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800235</v>
+        <v>124800237</v>
       </c>
       <c r="B7" t="n">
-        <v>91008</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1229,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1249,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>442902</v>
+        <v>442847</v>
       </c>
       <c r="R7" t="n">
-        <v>7000213</v>
+        <v>7000224</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800240</v>
+        <v>124800251</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1335,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1349,24 +1357,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442790</v>
+        <v>442674</v>
       </c>
       <c r="R8" t="n">
-        <v>7000196</v>
+        <v>7000138</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,10 +1425,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800251</v>
+        <v>124800244</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1441,21 +1441,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442674</v>
+        <v>442759</v>
       </c>
       <c r="R9" t="n">
-        <v>7000138</v>
+        <v>7000122</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800252</v>
+        <v>124800243</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1543,25 +1543,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442674</v>
+        <v>442768</v>
       </c>
       <c r="R10" t="n">
-        <v>7000139</v>
+        <v>7000121</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800242</v>
+        <v>124800249</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1653,21 +1653,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1675,24 +1675,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442778</v>
+        <v>442738</v>
       </c>
       <c r="R11" t="n">
-        <v>7000153</v>
+        <v>7000132</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1751,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800238</v>
+        <v>124800247</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>74906</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1767,21 +1759,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1789,24 +1781,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442812</v>
+        <v>442741</v>
       </c>
       <c r="R12" t="n">
-        <v>7000185</v>
+        <v>7000167</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,10 +1849,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800245</v>
+        <v>124800240</v>
       </c>
       <c r="B13" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1881,21 +1865,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1903,16 +1887,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442754</v>
+        <v>442790</v>
       </c>
       <c r="R13" t="n">
-        <v>7000189</v>
+        <v>7000196</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,10 +1963,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800239</v>
+        <v>124800242</v>
       </c>
       <c r="B14" t="n">
-        <v>74906</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1987,21 +1979,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2009,16 +2001,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442803</v>
+        <v>442778</v>
       </c>
       <c r="R14" t="n">
-        <v>7000212</v>
+        <v>7000153</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,10 +2077,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800244</v>
+        <v>124800246</v>
       </c>
       <c r="B15" t="n">
-        <v>91008</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2093,21 +2093,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442759</v>
+        <v>442748</v>
       </c>
       <c r="R15" t="n">
-        <v>7000122</v>
+        <v>7000187</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800237</v>
+        <v>124800238</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2199,21 +2199,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2221,16 +2221,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>442847</v>
+        <v>442812</v>
       </c>
       <c r="R16" t="n">
-        <v>7000224</v>
+        <v>7000185</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2289,10 +2297,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800243</v>
+        <v>124800234</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2301,25 +2309,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2333,10 +2341,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442768</v>
+        <v>442904</v>
       </c>
       <c r="R17" t="n">
-        <v>7000121</v>
+        <v>7000228</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,10 +2403,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800234</v>
+        <v>124800248</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2411,21 +2419,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2439,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442904</v>
+        <v>442739</v>
       </c>
       <c r="R18" t="n">
-        <v>7000228</v>
+        <v>7000176</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2501,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800241</v>
+        <v>124800250</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2517,21 +2525,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2539,24 +2547,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442785</v>
+        <v>442699</v>
       </c>
       <c r="R19" t="n">
-        <v>7000194</v>
+        <v>7000206</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800250</v>
+        <v>124800236</v>
       </c>
       <c r="B20" t="n">
-        <v>82597</v>
+        <v>91012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,21 +2631,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>442699</v>
+        <v>442848</v>
       </c>
       <c r="R20" t="n">
-        <v>7000206</v>
+        <v>7000225</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 23822-2024 artfynd.xlsx
+++ b/artfynd/A 23822-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124800241</v>
+        <v>124800252</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,24 +713,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442785</v>
+        <v>442674</v>
       </c>
       <c r="R2" t="n">
-        <v>7000194</v>
+        <v>7000139</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800252</v>
+        <v>124800241</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,16 +819,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442674</v>
+        <v>442785</v>
       </c>
       <c r="R3" t="n">
-        <v>7000139</v>
+        <v>7000194</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1637,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800249</v>
+        <v>124800242</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1653,21 +1653,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1675,16 +1675,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442738</v>
+        <v>442778</v>
       </c>
       <c r="R11" t="n">
-        <v>7000132</v>
+        <v>7000153</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,10 +1751,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800247</v>
+        <v>124800240</v>
       </c>
       <c r="B12" t="n">
-        <v>74906</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1759,21 +1767,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1781,16 +1789,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442741</v>
+        <v>442790</v>
       </c>
       <c r="R12" t="n">
-        <v>7000167</v>
+        <v>7000196</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,10 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800240</v>
+        <v>124800249</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1865,21 +1881,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1887,24 +1903,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442790</v>
+        <v>442738</v>
       </c>
       <c r="R13" t="n">
-        <v>7000196</v>
+        <v>7000132</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1963,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800242</v>
+        <v>124800247</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>74906</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1979,21 +1987,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2001,24 +2009,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442778</v>
+        <v>442741</v>
       </c>
       <c r="R14" t="n">
-        <v>7000153</v>
+        <v>7000167</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 23822-2024 artfynd.xlsx
+++ b/artfynd/A 23822-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124800252</v>
+        <v>124800236</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442674</v>
+        <v>442848</v>
       </c>
       <c r="R2" t="n">
-        <v>7000139</v>
+        <v>7000225</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800241</v>
+        <v>124800234</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -819,24 +819,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442785</v>
+        <v>442904</v>
       </c>
       <c r="R3" t="n">
-        <v>7000194</v>
+        <v>7000228</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800239</v>
+        <v>124800241</v>
       </c>
       <c r="B4" t="n">
-        <v>74906</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -933,16 +925,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442803</v>
+        <v>442785</v>
       </c>
       <c r="R4" t="n">
-        <v>7000212</v>
+        <v>7000194</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800235</v>
+        <v>124800239</v>
       </c>
       <c r="B5" t="n">
-        <v>91008</v>
+        <v>74906</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442902</v>
+        <v>442803</v>
       </c>
       <c r="R5" t="n">
-        <v>7000213</v>
+        <v>7000212</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800245</v>
+        <v>124800238</v>
       </c>
       <c r="B6" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,21 +1123,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1145,16 +1145,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>442754</v>
+        <v>442812</v>
       </c>
       <c r="R6" t="n">
-        <v>7000189</v>
+        <v>7000185</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800237</v>
+        <v>124800235</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,21 +1237,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1257,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>442847</v>
+        <v>442902</v>
       </c>
       <c r="R7" t="n">
-        <v>7000224</v>
+        <v>7000213</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800251</v>
+        <v>124800249</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1363,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442674</v>
+        <v>442738</v>
       </c>
       <c r="R8" t="n">
-        <v>7000138</v>
+        <v>7000132</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800244</v>
+        <v>124800240</v>
       </c>
       <c r="B9" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1441,21 +1449,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1463,16 +1471,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442759</v>
+        <v>442790</v>
       </c>
       <c r="R9" t="n">
-        <v>7000122</v>
+        <v>7000196</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,10 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800243</v>
+        <v>124800246</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1543,25 +1559,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1575,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442768</v>
+        <v>442748</v>
       </c>
       <c r="R10" t="n">
-        <v>7000121</v>
+        <v>7000187</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800242</v>
+        <v>124800237</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1653,21 +1669,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1675,24 +1691,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442778</v>
+        <v>442847</v>
       </c>
       <c r="R11" t="n">
-        <v>7000153</v>
+        <v>7000224</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1751,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800240</v>
+        <v>124800248</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1767,21 +1775,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1789,24 +1797,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442790</v>
+        <v>442739</v>
       </c>
       <c r="R12" t="n">
-        <v>7000196</v>
+        <v>7000176</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,10 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800249</v>
+        <v>124800247</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>74906</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1881,21 +1881,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442738</v>
+        <v>442741</v>
       </c>
       <c r="R13" t="n">
-        <v>7000132</v>
+        <v>7000167</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800247</v>
+        <v>124800243</v>
       </c>
       <c r="B14" t="n">
-        <v>74906</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,25 +1983,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1467</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442741</v>
+        <v>442768</v>
       </c>
       <c r="R14" t="n">
-        <v>7000167</v>
+        <v>7000121</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,10 +2077,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800246</v>
+        <v>124800250</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>82597</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2093,21 +2093,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442748</v>
+        <v>442699</v>
       </c>
       <c r="R15" t="n">
-        <v>7000187</v>
+        <v>7000206</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800238</v>
+        <v>124800251</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2199,21 +2199,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2221,24 +2221,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>442812</v>
+        <v>442674</v>
       </c>
       <c r="R16" t="n">
-        <v>7000185</v>
+        <v>7000138</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2297,10 +2289,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800234</v>
+        <v>124800245</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2313,21 +2305,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2341,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442904</v>
+        <v>442754</v>
       </c>
       <c r="R17" t="n">
-        <v>7000228</v>
+        <v>7000189</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2403,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800248</v>
+        <v>124800244</v>
       </c>
       <c r="B18" t="n">
-        <v>91299</v>
+        <v>91008</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2419,21 +2411,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2447,10 +2439,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442739</v>
+        <v>442759</v>
       </c>
       <c r="R18" t="n">
-        <v>7000176</v>
+        <v>7000122</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2509,10 +2501,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800250</v>
+        <v>124800252</v>
       </c>
       <c r="B19" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2525,21 +2517,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2553,10 +2545,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442699</v>
+        <v>442674</v>
       </c>
       <c r="R19" t="n">
-        <v>7000206</v>
+        <v>7000139</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2615,10 +2607,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800236</v>
+        <v>124800242</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,21 +2623,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2653,16 +2645,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>442848</v>
+        <v>442778</v>
       </c>
       <c r="R20" t="n">
-        <v>7000225</v>
+        <v>7000153</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 23822-2024 artfynd.xlsx
+++ b/artfynd/A 23822-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124800236</v>
+        <v>124800251</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442848</v>
+        <v>442674</v>
       </c>
       <c r="R2" t="n">
-        <v>7000225</v>
+        <v>7000138</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800234</v>
+        <v>124800245</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442904</v>
+        <v>442754</v>
       </c>
       <c r="R3" t="n">
-        <v>7000228</v>
+        <v>7000189</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800241</v>
+        <v>124800249</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -925,24 +925,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442785</v>
+        <v>442738</v>
       </c>
       <c r="R4" t="n">
-        <v>7000194</v>
+        <v>7000132</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800239</v>
+        <v>124800235</v>
       </c>
       <c r="B5" t="n">
-        <v>74906</v>
+        <v>91008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1045,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442803</v>
+        <v>442902</v>
       </c>
       <c r="R5" t="n">
-        <v>7000212</v>
+        <v>7000213</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800238</v>
+        <v>124800237</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1145,24 +1137,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>442812</v>
+        <v>442847</v>
       </c>
       <c r="R6" t="n">
-        <v>7000185</v>
+        <v>7000224</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800235</v>
+        <v>124800239</v>
       </c>
       <c r="B7" t="n">
-        <v>91008</v>
+        <v>74906</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1265,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>442902</v>
+        <v>442803</v>
       </c>
       <c r="R7" t="n">
-        <v>7000213</v>
+        <v>7000212</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800249</v>
+        <v>124800242</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1365,16 +1349,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442738</v>
+        <v>442778</v>
       </c>
       <c r="R8" t="n">
-        <v>7000132</v>
+        <v>7000153</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1547,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800246</v>
+        <v>124800241</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1563,21 +1555,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1585,16 +1577,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442748</v>
+        <v>442785</v>
       </c>
       <c r="R10" t="n">
-        <v>7000187</v>
+        <v>7000194</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800237</v>
+        <v>124800238</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,21 +1669,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1691,16 +1691,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442847</v>
+        <v>442812</v>
       </c>
       <c r="R11" t="n">
-        <v>7000224</v>
+        <v>7000185</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1759,10 +1767,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800248</v>
+        <v>124800236</v>
       </c>
       <c r="B12" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,21 +1783,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1803,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442739</v>
+        <v>442848</v>
       </c>
       <c r="R12" t="n">
-        <v>7000176</v>
+        <v>7000225</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,10 +1873,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800247</v>
+        <v>124800252</v>
       </c>
       <c r="B13" t="n">
-        <v>74906</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1881,21 +1889,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1909,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442741</v>
+        <v>442674</v>
       </c>
       <c r="R13" t="n">
-        <v>7000167</v>
+        <v>7000139</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800243</v>
+        <v>124800248</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,25 +1991,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2015,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442768</v>
+        <v>442739</v>
       </c>
       <c r="R14" t="n">
-        <v>7000121</v>
+        <v>7000176</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,10 +2085,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800250</v>
+        <v>124800246</v>
       </c>
       <c r="B15" t="n">
-        <v>82597</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2093,21 +2101,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2121,10 +2129,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442699</v>
+        <v>442748</v>
       </c>
       <c r="R15" t="n">
-        <v>7000206</v>
+        <v>7000187</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,10 +2191,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800251</v>
+        <v>124800250</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>82597</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2199,21 +2207,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2227,10 +2235,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>442674</v>
+        <v>442699</v>
       </c>
       <c r="R16" t="n">
-        <v>7000138</v>
+        <v>7000206</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2289,7 +2297,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800245</v>
+        <v>124800244</v>
       </c>
       <c r="B17" t="n">
         <v>91008</v>
@@ -2333,10 +2341,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442754</v>
+        <v>442759</v>
       </c>
       <c r="R17" t="n">
-        <v>7000189</v>
+        <v>7000122</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,10 +2403,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800244</v>
+        <v>124800243</v>
       </c>
       <c r="B18" t="n">
-        <v>91008</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2407,25 +2415,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2439,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442759</v>
+        <v>442768</v>
       </c>
       <c r="R18" t="n">
-        <v>7000122</v>
+        <v>7000121</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2501,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800252</v>
+        <v>124800247</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>74906</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2517,21 +2525,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2545,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442674</v>
+        <v>442741</v>
       </c>
       <c r="R19" t="n">
-        <v>7000139</v>
+        <v>7000167</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2607,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800242</v>
+        <v>124800234</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2623,21 +2631,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2645,24 +2653,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>442778</v>
+        <v>442904</v>
       </c>
       <c r="R20" t="n">
-        <v>7000153</v>
+        <v>7000228</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 23822-2024 artfynd.xlsx
+++ b/artfynd/A 23822-2024 artfynd.xlsx
@@ -1873,10 +1873,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800252</v>
+        <v>124800248</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1889,21 +1889,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442674</v>
+        <v>442739</v>
       </c>
       <c r="R13" t="n">
-        <v>7000139</v>
+        <v>7000176</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800248</v>
+        <v>124800252</v>
       </c>
       <c r="B14" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1995,21 +1995,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442739</v>
+        <v>442674</v>
       </c>
       <c r="R14" t="n">
-        <v>7000176</v>
+        <v>7000139</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 23822-2024 artfynd.xlsx
+++ b/artfynd/A 23822-2024 artfynd.xlsx
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800239</v>
+        <v>124800242</v>
       </c>
       <c r="B7" t="n">
-        <v>74906</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1243,16 +1243,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>442803</v>
+        <v>442778</v>
       </c>
       <c r="R7" t="n">
-        <v>7000212</v>
+        <v>7000153</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,7 +1319,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800242</v>
+        <v>124800240</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1363,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442778</v>
+        <v>442790</v>
       </c>
       <c r="R8" t="n">
-        <v>7000153</v>
+        <v>7000196</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800240</v>
+        <v>124800239</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>74906</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1441,21 +1449,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1463,24 +1471,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442790</v>
+        <v>442803</v>
       </c>
       <c r="R9" t="n">
-        <v>7000196</v>
+        <v>7000212</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1873,10 +1873,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800248</v>
+        <v>124800252</v>
       </c>
       <c r="B13" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1889,21 +1889,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442739</v>
+        <v>442674</v>
       </c>
       <c r="R13" t="n">
-        <v>7000176</v>
+        <v>7000139</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800252</v>
+        <v>124800248</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1995,21 +1995,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442674</v>
+        <v>442739</v>
       </c>
       <c r="R14" t="n">
-        <v>7000139</v>
+        <v>7000176</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 23822-2024 artfynd.xlsx
+++ b/artfynd/A 23822-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124800251</v>
+        <v>124800240</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,16 +713,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442674</v>
+        <v>442790</v>
       </c>
       <c r="R2" t="n">
-        <v>7000138</v>
+        <v>7000196</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -887,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800249</v>
+        <v>124800243</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +907,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442738</v>
+        <v>442768</v>
       </c>
       <c r="R4" t="n">
-        <v>7000132</v>
+        <v>7000121</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800235</v>
+        <v>124800252</v>
       </c>
       <c r="B5" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442902</v>
+        <v>442674</v>
       </c>
       <c r="R5" t="n">
-        <v>7000213</v>
+        <v>7000139</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800237</v>
+        <v>124800248</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1123,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>442847</v>
+        <v>442739</v>
       </c>
       <c r="R6" t="n">
-        <v>7000224</v>
+        <v>7000176</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800242</v>
+        <v>124800239</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>74906</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1229,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1243,24 +1251,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>442778</v>
+        <v>442803</v>
       </c>
       <c r="R7" t="n">
-        <v>7000153</v>
+        <v>7000212</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800240</v>
+        <v>124800234</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1335,21 +1335,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1357,24 +1357,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442790</v>
+        <v>442904</v>
       </c>
       <c r="R8" t="n">
-        <v>7000196</v>
+        <v>7000228</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,10 +1425,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800239</v>
+        <v>124800241</v>
       </c>
       <c r="B9" t="n">
-        <v>74906</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,21 +1441,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1471,16 +1463,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442803</v>
+        <v>442785</v>
       </c>
       <c r="R9" t="n">
-        <v>7000212</v>
+        <v>7000194</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800241</v>
+        <v>124800244</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1555,21 +1555,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1577,24 +1577,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442785</v>
+        <v>442759</v>
       </c>
       <c r="R10" t="n">
-        <v>7000194</v>
+        <v>7000122</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,10 +1645,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800238</v>
+        <v>124800236</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,21 +1661,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1691,24 +1683,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442812</v>
+        <v>442848</v>
       </c>
       <c r="R11" t="n">
-        <v>7000185</v>
+        <v>7000225</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1767,10 +1751,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800236</v>
+        <v>124800247</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>74906</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1783,21 +1767,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1811,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442848</v>
+        <v>442741</v>
       </c>
       <c r="R12" t="n">
-        <v>7000225</v>
+        <v>7000167</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800252</v>
+        <v>124800242</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1889,21 +1873,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1911,16 +1895,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442674</v>
+        <v>442778</v>
       </c>
       <c r="R13" t="n">
-        <v>7000139</v>
+        <v>7000153</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800248</v>
+        <v>124800249</v>
       </c>
       <c r="B14" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1995,21 +1987,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2023,10 +2015,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442739</v>
+        <v>442738</v>
       </c>
       <c r="R14" t="n">
-        <v>7000176</v>
+        <v>7000132</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2085,10 +2077,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800246</v>
+        <v>124800235</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2101,21 +2093,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2129,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442748</v>
+        <v>442902</v>
       </c>
       <c r="R15" t="n">
-        <v>7000187</v>
+        <v>7000213</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2191,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800250</v>
+        <v>124800238</v>
       </c>
       <c r="B16" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2207,21 +2199,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2229,16 +2221,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>442699</v>
+        <v>442812</v>
       </c>
       <c r="R16" t="n">
-        <v>7000206</v>
+        <v>7000185</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2297,10 +2297,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800244</v>
+        <v>124800251</v>
       </c>
       <c r="B17" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2313,21 +2313,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442759</v>
+        <v>442674</v>
       </c>
       <c r="R17" t="n">
-        <v>7000122</v>
+        <v>7000138</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2403,10 +2403,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800243</v>
+        <v>124800237</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2415,25 +2415,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442768</v>
+        <v>442847</v>
       </c>
       <c r="R18" t="n">
-        <v>7000121</v>
+        <v>7000224</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2509,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800247</v>
+        <v>124800246</v>
       </c>
       <c r="B19" t="n">
-        <v>74906</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2525,21 +2525,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1467</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442741</v>
+        <v>442748</v>
       </c>
       <c r="R19" t="n">
-        <v>7000167</v>
+        <v>7000187</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800234</v>
+        <v>124800250</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>82597</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,21 +2631,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>442904</v>
+        <v>442699</v>
       </c>
       <c r="R20" t="n">
-        <v>7000228</v>
+        <v>7000206</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 23822-2024 artfynd.xlsx
+++ b/artfynd/A 23822-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124800240</v>
+        <v>124800244</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,24 +713,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442790</v>
+        <v>442759</v>
       </c>
       <c r="R2" t="n">
-        <v>7000196</v>
+        <v>7000122</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800245</v>
+        <v>124800237</v>
       </c>
       <c r="B3" t="n">
-        <v>91008</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -833,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442754</v>
+        <v>442847</v>
       </c>
       <c r="R3" t="n">
-        <v>7000189</v>
+        <v>7000224</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800243</v>
+        <v>124800248</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442768</v>
+        <v>442739</v>
       </c>
       <c r="R4" t="n">
-        <v>7000121</v>
+        <v>7000176</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800252</v>
+        <v>124800241</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1039,16 +1031,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442674</v>
+        <v>442785</v>
       </c>
       <c r="R5" t="n">
-        <v>7000139</v>
+        <v>7000194</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800248</v>
+        <v>124800250</v>
       </c>
       <c r="B6" t="n">
-        <v>91299</v>
+        <v>82597</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,21 +1123,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>442739</v>
+        <v>442699</v>
       </c>
       <c r="R6" t="n">
-        <v>7000176</v>
+        <v>7000206</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800239</v>
+        <v>124800235</v>
       </c>
       <c r="B7" t="n">
-        <v>74906</v>
+        <v>91008</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,21 +1229,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>442803</v>
+        <v>442902</v>
       </c>
       <c r="R7" t="n">
-        <v>7000212</v>
+        <v>7000213</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800234</v>
+        <v>124800251</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1335,21 +1335,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442904</v>
+        <v>442674</v>
       </c>
       <c r="R8" t="n">
-        <v>7000228</v>
+        <v>7000138</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,10 +1425,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800241</v>
+        <v>124800245</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1441,21 +1441,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1463,24 +1463,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442785</v>
+        <v>442754</v>
       </c>
       <c r="R9" t="n">
-        <v>7000194</v>
+        <v>7000189</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800244</v>
+        <v>124800238</v>
       </c>
       <c r="B10" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1555,21 +1547,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1577,16 +1569,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442759</v>
+        <v>442812</v>
       </c>
       <c r="R10" t="n">
-        <v>7000122</v>
+        <v>7000185</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800236</v>
+        <v>124800252</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442848</v>
+        <v>442674</v>
       </c>
       <c r="R11" t="n">
-        <v>7000225</v>
+        <v>7000139</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800247</v>
+        <v>124800246</v>
       </c>
       <c r="B12" t="n">
-        <v>74906</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1767,21 +1767,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1467</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442741</v>
+        <v>442748</v>
       </c>
       <c r="R12" t="n">
-        <v>7000167</v>
+        <v>7000187</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800242</v>
+        <v>124800249</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,21 +1873,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1895,24 +1895,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442778</v>
+        <v>442738</v>
       </c>
       <c r="R13" t="n">
-        <v>7000153</v>
+        <v>7000132</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,10 +1963,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800249</v>
+        <v>124800234</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1987,21 +1979,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2015,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442738</v>
+        <v>442904</v>
       </c>
       <c r="R14" t="n">
-        <v>7000132</v>
+        <v>7000228</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,10 +2069,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800235</v>
+        <v>124800239</v>
       </c>
       <c r="B15" t="n">
-        <v>91008</v>
+        <v>74906</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2093,21 +2085,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2121,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442902</v>
+        <v>442803</v>
       </c>
       <c r="R15" t="n">
-        <v>7000213</v>
+        <v>7000212</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,10 +2175,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800238</v>
+        <v>124800243</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2195,25 +2187,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2221,24 +2213,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>442812</v>
+        <v>442768</v>
       </c>
       <c r="R16" t="n">
-        <v>7000185</v>
+        <v>7000121</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2297,10 +2281,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800251</v>
+        <v>124800236</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2313,21 +2297,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2341,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442674</v>
+        <v>442848</v>
       </c>
       <c r="R17" t="n">
-        <v>7000138</v>
+        <v>7000225</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2403,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800237</v>
+        <v>124800247</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>74906</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2419,21 +2403,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2447,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442847</v>
+        <v>442741</v>
       </c>
       <c r="R18" t="n">
-        <v>7000224</v>
+        <v>7000167</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2509,10 +2493,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800246</v>
+        <v>124800240</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2525,21 +2509,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2547,16 +2531,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442748</v>
+        <v>442790</v>
       </c>
       <c r="R19" t="n">
-        <v>7000187</v>
+        <v>7000196</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2615,10 +2607,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800250</v>
+        <v>124800242</v>
       </c>
       <c r="B20" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,21 +2623,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2653,16 +2645,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>442699</v>
+        <v>442778</v>
       </c>
       <c r="R20" t="n">
-        <v>7000206</v>
+        <v>7000153</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 23822-2024 artfynd.xlsx
+++ b/artfynd/A 23822-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124800244</v>
+        <v>124800241</v>
       </c>
       <c r="B2" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,16 +713,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442759</v>
+        <v>442785</v>
       </c>
       <c r="R2" t="n">
-        <v>7000122</v>
+        <v>7000194</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800237</v>
+        <v>124800250</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>82597</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +805,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442847</v>
+        <v>442699</v>
       </c>
       <c r="R3" t="n">
-        <v>7000224</v>
+        <v>7000206</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800248</v>
+        <v>124800247</v>
       </c>
       <c r="B4" t="n">
-        <v>91299</v>
+        <v>74906</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1467</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442739</v>
+        <v>442741</v>
       </c>
       <c r="R4" t="n">
-        <v>7000176</v>
+        <v>7000167</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800241</v>
+        <v>124800249</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1031,24 +1039,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442785</v>
+        <v>442738</v>
       </c>
       <c r="R5" t="n">
-        <v>7000194</v>
+        <v>7000132</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800250</v>
+        <v>124800242</v>
       </c>
       <c r="B6" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,21 +1123,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1145,16 +1145,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>442699</v>
+        <v>442778</v>
       </c>
       <c r="R6" t="n">
-        <v>7000206</v>
+        <v>7000153</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800235</v>
+        <v>124800236</v>
       </c>
       <c r="B7" t="n">
-        <v>91008</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,21 +1237,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1257,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>442902</v>
+        <v>442848</v>
       </c>
       <c r="R7" t="n">
-        <v>7000213</v>
+        <v>7000225</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800251</v>
+        <v>124800240</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1335,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1357,16 +1365,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442674</v>
+        <v>442790</v>
       </c>
       <c r="R8" t="n">
-        <v>7000138</v>
+        <v>7000196</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1531,10 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800238</v>
+        <v>124800243</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1543,25 +1559,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1569,24 +1585,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442812</v>
+        <v>442768</v>
       </c>
       <c r="R10" t="n">
-        <v>7000185</v>
+        <v>7000121</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1751,7 +1759,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800246</v>
+        <v>124800234</v>
       </c>
       <c r="B12" t="n">
         <v>91012</v>
@@ -1795,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442748</v>
+        <v>442904</v>
       </c>
       <c r="R12" t="n">
-        <v>7000187</v>
+        <v>7000228</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,10 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800249</v>
+        <v>124800239</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>74906</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,21 +1881,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1901,10 +1909,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442738</v>
+        <v>442803</v>
       </c>
       <c r="R13" t="n">
-        <v>7000132</v>
+        <v>7000212</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1963,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800234</v>
+        <v>124800248</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1979,21 +1987,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2007,10 +2015,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442904</v>
+        <v>442739</v>
       </c>
       <c r="R14" t="n">
-        <v>7000228</v>
+        <v>7000176</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2069,10 +2077,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800239</v>
+        <v>124800246</v>
       </c>
       <c r="B15" t="n">
-        <v>74906</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,21 +2093,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1467</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2113,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442803</v>
+        <v>442748</v>
       </c>
       <c r="R15" t="n">
-        <v>7000212</v>
+        <v>7000187</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800243</v>
+        <v>124800244</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>91008</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2187,25 +2195,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2219,10 +2227,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>442768</v>
+        <v>442759</v>
       </c>
       <c r="R16" t="n">
-        <v>7000121</v>
+        <v>7000122</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2281,10 +2289,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800236</v>
+        <v>124800251</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2297,21 +2305,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2325,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442848</v>
+        <v>442674</v>
       </c>
       <c r="R17" t="n">
-        <v>7000225</v>
+        <v>7000138</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800247</v>
+        <v>124800238</v>
       </c>
       <c r="B18" t="n">
-        <v>74906</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2403,21 +2411,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2425,16 +2433,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442741</v>
+        <v>442812</v>
       </c>
       <c r="R18" t="n">
-        <v>7000167</v>
+        <v>7000185</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2493,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800240</v>
+        <v>124800237</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2509,21 +2525,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2531,24 +2547,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442790</v>
+        <v>442847</v>
       </c>
       <c r="R19" t="n">
-        <v>7000196</v>
+        <v>7000224</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2607,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800242</v>
+        <v>124800235</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2623,21 +2631,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2645,24 +2653,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>442778</v>
+        <v>442902</v>
       </c>
       <c r="R20" t="n">
-        <v>7000153</v>
+        <v>7000213</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 23822-2024 artfynd.xlsx
+++ b/artfynd/A 23822-2024 artfynd.xlsx
@@ -1759,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800234</v>
+        <v>124800239</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>74906</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,21 +1775,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442904</v>
+        <v>442803</v>
       </c>
       <c r="R12" t="n">
-        <v>7000228</v>
+        <v>7000212</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,10 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800239</v>
+        <v>124800234</v>
       </c>
       <c r="B13" t="n">
-        <v>74906</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1881,21 +1881,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1467</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442803</v>
+        <v>442904</v>
       </c>
       <c r="R13" t="n">
-        <v>7000212</v>
+        <v>7000228</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2509,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800237</v>
+        <v>124800235</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2525,21 +2525,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442847</v>
+        <v>442902</v>
       </c>
       <c r="R19" t="n">
-        <v>7000224</v>
+        <v>7000213</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800235</v>
+        <v>124800237</v>
       </c>
       <c r="B20" t="n">
-        <v>91008</v>
+        <v>91012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,21 +2631,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>442902</v>
+        <v>442847</v>
       </c>
       <c r="R20" t="n">
-        <v>7000213</v>
+        <v>7000224</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 23822-2024 artfynd.xlsx
+++ b/artfynd/A 23822-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124800241</v>
+        <v>124800252</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,24 +713,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442785</v>
+        <v>442674</v>
       </c>
       <c r="R2" t="n">
-        <v>7000194</v>
+        <v>7000139</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800250</v>
+        <v>124800245</v>
       </c>
       <c r="B3" t="n">
-        <v>82597</v>
+        <v>91008</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -833,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442699</v>
+        <v>442754</v>
       </c>
       <c r="R3" t="n">
-        <v>7000206</v>
+        <v>7000189</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800247</v>
+        <v>124800242</v>
       </c>
       <c r="B4" t="n">
-        <v>74906</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -933,16 +925,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442741</v>
+        <v>442778</v>
       </c>
       <c r="R4" t="n">
-        <v>7000167</v>
+        <v>7000153</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800249</v>
+        <v>124800251</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442738</v>
+        <v>442674</v>
       </c>
       <c r="R5" t="n">
-        <v>7000132</v>
+        <v>7000138</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800242</v>
+        <v>124800249</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,21 +1123,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1145,24 +1145,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>442778</v>
+        <v>442738</v>
       </c>
       <c r="R6" t="n">
-        <v>7000153</v>
+        <v>7000132</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800236</v>
+        <v>124800241</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,21 +1229,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1259,16 +1251,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>442848</v>
+        <v>442785</v>
       </c>
       <c r="R7" t="n">
-        <v>7000225</v>
+        <v>7000194</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800240</v>
+        <v>124800246</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1365,24 +1365,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442790</v>
+        <v>442748</v>
       </c>
       <c r="R8" t="n">
-        <v>7000196</v>
+        <v>7000187</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800245</v>
+        <v>124800239</v>
       </c>
       <c r="B9" t="n">
-        <v>91008</v>
+        <v>74906</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1457,21 +1449,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1485,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442754</v>
+        <v>442803</v>
       </c>
       <c r="R9" t="n">
-        <v>7000189</v>
+        <v>7000212</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800243</v>
+        <v>124800240</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,25 +1551,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1585,16 +1577,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442768</v>
+        <v>442790</v>
       </c>
       <c r="R10" t="n">
-        <v>7000121</v>
+        <v>7000196</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800252</v>
+        <v>124800235</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,21 +1669,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442674</v>
+        <v>442902</v>
       </c>
       <c r="R11" t="n">
-        <v>7000139</v>
+        <v>7000213</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1759,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800239</v>
+        <v>124800237</v>
       </c>
       <c r="B12" t="n">
-        <v>74906</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,21 +1775,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1467</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442803</v>
+        <v>442847</v>
       </c>
       <c r="R12" t="n">
-        <v>7000212</v>
+        <v>7000224</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,7 +1865,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800234</v>
+        <v>124800236</v>
       </c>
       <c r="B13" t="n">
         <v>91012</v>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442904</v>
+        <v>442848</v>
       </c>
       <c r="R13" t="n">
-        <v>7000228</v>
+        <v>7000225</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800248</v>
+        <v>124800243</v>
       </c>
       <c r="B14" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,25 +1983,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442739</v>
+        <v>442768</v>
       </c>
       <c r="R14" t="n">
-        <v>7000176</v>
+        <v>7000121</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,10 +2077,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800246</v>
+        <v>124800244</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2093,21 +2093,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442748</v>
+        <v>442759</v>
       </c>
       <c r="R15" t="n">
-        <v>7000187</v>
+        <v>7000122</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800244</v>
+        <v>124800250</v>
       </c>
       <c r="B16" t="n">
-        <v>91008</v>
+        <v>82597</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2199,21 +2199,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2227,10 +2227,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>442759</v>
+        <v>442699</v>
       </c>
       <c r="R16" t="n">
-        <v>7000122</v>
+        <v>7000206</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2289,10 +2289,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800251</v>
+        <v>124800234</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2305,21 +2305,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442674</v>
+        <v>442904</v>
       </c>
       <c r="R17" t="n">
-        <v>7000138</v>
+        <v>7000228</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2509,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800235</v>
+        <v>124800248</v>
       </c>
       <c r="B19" t="n">
-        <v>91008</v>
+        <v>91299</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2525,21 +2525,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442902</v>
+        <v>442739</v>
       </c>
       <c r="R19" t="n">
-        <v>7000213</v>
+        <v>7000176</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800237</v>
+        <v>124800247</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>74906</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,21 +2631,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>442847</v>
+        <v>442741</v>
       </c>
       <c r="R20" t="n">
-        <v>7000224</v>
+        <v>7000167</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 23822-2024 artfynd.xlsx
+++ b/artfynd/A 23822-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800245</v>
+        <v>124800251</v>
       </c>
       <c r="B3" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442754</v>
+        <v>442674</v>
       </c>
       <c r="R3" t="n">
-        <v>7000189</v>
+        <v>7000138</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800242</v>
+        <v>124800237</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -925,24 +925,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442778</v>
+        <v>442847</v>
       </c>
       <c r="R4" t="n">
-        <v>7000153</v>
+        <v>7000224</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800251</v>
+        <v>124800238</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1039,16 +1031,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442674</v>
+        <v>442812</v>
       </c>
       <c r="R5" t="n">
-        <v>7000138</v>
+        <v>7000185</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800249</v>
+        <v>124800246</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,21 +1123,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>442738</v>
+        <v>442748</v>
       </c>
       <c r="R6" t="n">
-        <v>7000132</v>
+        <v>7000187</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800241</v>
+        <v>124800234</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,21 +1229,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1251,24 +1251,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>442785</v>
+        <v>442904</v>
       </c>
       <c r="R7" t="n">
-        <v>7000194</v>
+        <v>7000228</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800246</v>
+        <v>124800235</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,21 +1335,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1371,10 +1363,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442748</v>
+        <v>442902</v>
       </c>
       <c r="R8" t="n">
-        <v>7000187</v>
+        <v>7000213</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1539,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800240</v>
+        <v>124800243</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1551,25 +1543,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1577,24 +1569,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442790</v>
+        <v>442768</v>
       </c>
       <c r="R10" t="n">
-        <v>7000196</v>
+        <v>7000121</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800235</v>
+        <v>124800249</v>
       </c>
       <c r="B11" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,21 +1653,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1697,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442902</v>
+        <v>442738</v>
       </c>
       <c r="R11" t="n">
-        <v>7000213</v>
+        <v>7000132</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1759,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800237</v>
+        <v>124800247</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>74906</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,21 +1759,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1803,10 +1787,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442847</v>
+        <v>442741</v>
       </c>
       <c r="R12" t="n">
-        <v>7000224</v>
+        <v>7000167</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,10 +1849,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800236</v>
+        <v>124800248</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1881,21 +1865,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1909,10 +1893,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442848</v>
+        <v>442739</v>
       </c>
       <c r="R13" t="n">
-        <v>7000225</v>
+        <v>7000176</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,10 +1955,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800243</v>
+        <v>124800240</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,25 +1967,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2009,16 +1993,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442768</v>
+        <v>442790</v>
       </c>
       <c r="R14" t="n">
-        <v>7000121</v>
+        <v>7000196</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,10 +2069,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800244</v>
+        <v>124800250</v>
       </c>
       <c r="B15" t="n">
-        <v>91008</v>
+        <v>82597</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2093,21 +2085,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2121,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442759</v>
+        <v>442699</v>
       </c>
       <c r="R15" t="n">
-        <v>7000122</v>
+        <v>7000206</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,10 +2175,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800250</v>
+        <v>124800245</v>
       </c>
       <c r="B16" t="n">
-        <v>82597</v>
+        <v>91008</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2199,21 +2191,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2227,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>442699</v>
+        <v>442754</v>
       </c>
       <c r="R16" t="n">
-        <v>7000206</v>
+        <v>7000189</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2289,10 +2281,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800234</v>
+        <v>124800242</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2305,21 +2297,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2327,16 +2319,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442904</v>
+        <v>442778</v>
       </c>
       <c r="R17" t="n">
-        <v>7000228</v>
+        <v>7000153</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,7 +2395,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800238</v>
+        <v>124800241</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442812</v>
+        <v>442785</v>
       </c>
       <c r="R18" t="n">
-        <v>7000185</v>
+        <v>7000194</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2509,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800248</v>
+        <v>124800236</v>
       </c>
       <c r="B19" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2525,21 +2525,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442739</v>
+        <v>442848</v>
       </c>
       <c r="R19" t="n">
-        <v>7000176</v>
+        <v>7000225</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800247</v>
+        <v>124800244</v>
       </c>
       <c r="B20" t="n">
-        <v>74906</v>
+        <v>91008</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,21 +2631,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>442741</v>
+        <v>442759</v>
       </c>
       <c r="R20" t="n">
-        <v>7000167</v>
+        <v>7000122</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 23822-2024 artfynd.xlsx
+++ b/artfynd/A 23822-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124800252</v>
+        <v>124800240</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,16 +713,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442674</v>
+        <v>442790</v>
       </c>
       <c r="R2" t="n">
-        <v>7000139</v>
+        <v>7000196</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800251</v>
+        <v>124800236</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>91166</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +805,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442674</v>
+        <v>442848</v>
       </c>
       <c r="R3" t="n">
-        <v>7000138</v>
+        <v>7000225</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800237</v>
+        <v>124800250</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>82737</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442847</v>
+        <v>442699</v>
       </c>
       <c r="R4" t="n">
-        <v>7000224</v>
+        <v>7000206</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800238</v>
+        <v>124800247</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>75030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1031,24 +1039,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442812</v>
+        <v>442741</v>
       </c>
       <c r="R5" t="n">
-        <v>7000185</v>
+        <v>7000167</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800246</v>
+        <v>124800249</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>78947</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,21 +1123,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>442748</v>
+        <v>442738</v>
       </c>
       <c r="R6" t="n">
-        <v>7000187</v>
+        <v>7000132</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800234</v>
+        <v>124800238</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>57635</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,21 +1229,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1251,16 +1251,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>442904</v>
+        <v>442812</v>
       </c>
       <c r="R7" t="n">
-        <v>7000228</v>
+        <v>7000185</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800235</v>
+        <v>124800246</v>
       </c>
       <c r="B8" t="n">
-        <v>91008</v>
+        <v>91166</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1335,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1363,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442902</v>
+        <v>442748</v>
       </c>
       <c r="R8" t="n">
-        <v>7000213</v>
+        <v>7000187</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800239</v>
+        <v>124800244</v>
       </c>
       <c r="B9" t="n">
-        <v>74906</v>
+        <v>91162</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1441,21 +1449,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1469,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442803</v>
+        <v>442759</v>
       </c>
       <c r="R9" t="n">
-        <v>7000212</v>
+        <v>7000122</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800243</v>
+        <v>124800252</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>78947</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1543,25 +1551,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1575,10 +1583,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442768</v>
+        <v>442674</v>
       </c>
       <c r="R10" t="n">
-        <v>7000121</v>
+        <v>7000139</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,10 +1645,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800249</v>
+        <v>124800248</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>91459</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1653,21 +1661,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1681,10 +1689,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442738</v>
+        <v>442739</v>
       </c>
       <c r="R11" t="n">
-        <v>7000132</v>
+        <v>7000176</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,10 +1751,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800247</v>
+        <v>124800239</v>
       </c>
       <c r="B12" t="n">
-        <v>74906</v>
+        <v>75030</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1787,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442741</v>
+        <v>442803</v>
       </c>
       <c r="R12" t="n">
-        <v>7000167</v>
+        <v>7000212</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800248</v>
+        <v>124800242</v>
       </c>
       <c r="B13" t="n">
-        <v>91299</v>
+        <v>57635</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1865,21 +1873,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1887,16 +1895,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442739</v>
+        <v>442778</v>
       </c>
       <c r="R13" t="n">
-        <v>7000176</v>
+        <v>7000153</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1955,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800240</v>
+        <v>124800251</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1971,21 +1987,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1993,24 +2009,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442790</v>
+        <v>442674</v>
       </c>
       <c r="R14" t="n">
-        <v>7000196</v>
+        <v>7000138</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2069,10 +2077,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800250</v>
+        <v>124800237</v>
       </c>
       <c r="B15" t="n">
-        <v>82597</v>
+        <v>91166</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,21 +2093,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2113,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442699</v>
+        <v>442847</v>
       </c>
       <c r="R15" t="n">
-        <v>7000206</v>
+        <v>7000224</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2178,7 +2186,7 @@
         <v>124800245</v>
       </c>
       <c r="B16" t="n">
-        <v>91008</v>
+        <v>91162</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2281,10 +2289,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800242</v>
+        <v>124800241</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2333,10 +2341,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442778</v>
+        <v>442785</v>
       </c>
       <c r="R17" t="n">
-        <v>7000153</v>
+        <v>7000194</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,10 +2403,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800241</v>
+        <v>124800234</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>91166</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2411,21 +2419,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2433,24 +2441,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442785</v>
+        <v>442904</v>
       </c>
       <c r="R18" t="n">
-        <v>7000194</v>
+        <v>7000228</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2509,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800236</v>
+        <v>124800235</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>91162</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2525,21 +2525,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442848</v>
+        <v>442902</v>
       </c>
       <c r="R19" t="n">
-        <v>7000225</v>
+        <v>7000213</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800244</v>
+        <v>124800243</v>
       </c>
       <c r="B20" t="n">
-        <v>91008</v>
+        <v>98269</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2627,25 +2627,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>442759</v>
+        <v>442768</v>
       </c>
       <c r="R20" t="n">
-        <v>7000122</v>
+        <v>7000121</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 23822-2024 artfynd.xlsx
+++ b/artfynd/A 23822-2024 artfynd.xlsx
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800246</v>
+        <v>124800248</v>
       </c>
       <c r="B8" t="n">
-        <v>91166</v>
+        <v>91459</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442748</v>
+        <v>442739</v>
       </c>
       <c r="R8" t="n">
-        <v>7000187</v>
+        <v>7000176</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800244</v>
+        <v>124800246</v>
       </c>
       <c r="B9" t="n">
-        <v>91162</v>
+        <v>91166</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,21 +1449,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442759</v>
+        <v>442748</v>
       </c>
       <c r="R9" t="n">
-        <v>7000122</v>
+        <v>7000187</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800252</v>
+        <v>124800244</v>
       </c>
       <c r="B10" t="n">
-        <v>78947</v>
+        <v>91162</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1555,21 +1555,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442674</v>
+        <v>442759</v>
       </c>
       <c r="R10" t="n">
-        <v>7000139</v>
+        <v>7000122</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800248</v>
+        <v>124800252</v>
       </c>
       <c r="B11" t="n">
-        <v>91459</v>
+        <v>78947</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442739</v>
+        <v>442674</v>
       </c>
       <c r="R11" t="n">
-        <v>7000176</v>
+        <v>7000139</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 23822-2024 artfynd.xlsx
+++ b/artfynd/A 23822-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124800240</v>
+        <v>124800249</v>
       </c>
       <c r="B2" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,24 +713,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442790</v>
+        <v>442738</v>
       </c>
       <c r="R2" t="n">
-        <v>7000196</v>
+        <v>7000132</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800236</v>
+        <v>124800241</v>
       </c>
       <c r="B3" t="n">
-        <v>91166</v>
+        <v>57635</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,16 +819,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442848</v>
+        <v>442785</v>
       </c>
       <c r="R3" t="n">
-        <v>7000225</v>
+        <v>7000194</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800247</v>
+        <v>124800243</v>
       </c>
       <c r="B5" t="n">
-        <v>75030</v>
+        <v>98269</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,25 +1013,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1467</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442741</v>
+        <v>442768</v>
       </c>
       <c r="R5" t="n">
-        <v>7000167</v>
+        <v>7000121</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800249</v>
+        <v>124800247</v>
       </c>
       <c r="B6" t="n">
-        <v>78947</v>
+        <v>75030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,21 +1123,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>442738</v>
+        <v>442741</v>
       </c>
       <c r="R6" t="n">
-        <v>7000132</v>
+        <v>7000167</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800238</v>
+        <v>124800237</v>
       </c>
       <c r="B7" t="n">
-        <v>57635</v>
+        <v>91166</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,21 +1229,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1251,24 +1251,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>442812</v>
+        <v>442847</v>
       </c>
       <c r="R7" t="n">
-        <v>7000185</v>
+        <v>7000224</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800248</v>
+        <v>124800252</v>
       </c>
       <c r="B8" t="n">
-        <v>91459</v>
+        <v>78947</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,21 +1335,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1371,10 +1363,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442739</v>
+        <v>442674</v>
       </c>
       <c r="R8" t="n">
-        <v>7000176</v>
+        <v>7000139</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,7 +1425,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800246</v>
+        <v>124800236</v>
       </c>
       <c r="B9" t="n">
         <v>91166</v>
@@ -1477,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442748</v>
+        <v>442848</v>
       </c>
       <c r="R9" t="n">
-        <v>7000187</v>
+        <v>7000225</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800244</v>
+        <v>124800234</v>
       </c>
       <c r="B10" t="n">
-        <v>91162</v>
+        <v>91166</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1555,21 +1547,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1583,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442759</v>
+        <v>442904</v>
       </c>
       <c r="R10" t="n">
-        <v>7000122</v>
+        <v>7000228</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1645,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800252</v>
+        <v>124800246</v>
       </c>
       <c r="B11" t="n">
-        <v>78947</v>
+        <v>91166</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1661,21 +1653,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1689,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442674</v>
+        <v>442748</v>
       </c>
       <c r="R11" t="n">
-        <v>7000139</v>
+        <v>7000187</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1971,10 +1963,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800251</v>
+        <v>124800238</v>
       </c>
       <c r="B14" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1987,21 +1979,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2009,16 +2001,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442674</v>
+        <v>442812</v>
       </c>
       <c r="R14" t="n">
-        <v>7000138</v>
+        <v>7000185</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,10 +2077,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800237</v>
+        <v>124800248</v>
       </c>
       <c r="B15" t="n">
-        <v>91166</v>
+        <v>91459</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2093,21 +2093,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442847</v>
+        <v>442739</v>
       </c>
       <c r="R15" t="n">
-        <v>7000224</v>
+        <v>7000176</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800245</v>
+        <v>124800240</v>
       </c>
       <c r="B16" t="n">
-        <v>91162</v>
+        <v>57635</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2199,21 +2199,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2221,16 +2221,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>442754</v>
+        <v>442790</v>
       </c>
       <c r="R16" t="n">
-        <v>7000189</v>
+        <v>7000196</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2289,10 +2297,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800241</v>
+        <v>124800251</v>
       </c>
       <c r="B17" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2305,21 +2313,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2327,24 +2335,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442785</v>
+        <v>442674</v>
       </c>
       <c r="R17" t="n">
-        <v>7000194</v>
+        <v>7000138</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2403,10 +2403,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800234</v>
+        <v>124800244</v>
       </c>
       <c r="B18" t="n">
-        <v>91166</v>
+        <v>91162</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2419,21 +2419,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442904</v>
+        <v>442759</v>
       </c>
       <c r="R18" t="n">
-        <v>7000228</v>
+        <v>7000122</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2509,7 +2509,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800235</v>
+        <v>124800245</v>
       </c>
       <c r="B19" t="n">
         <v>91162</v>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442902</v>
+        <v>442754</v>
       </c>
       <c r="R19" t="n">
-        <v>7000213</v>
+        <v>7000189</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800243</v>
+        <v>124800235</v>
       </c>
       <c r="B20" t="n">
-        <v>98269</v>
+        <v>91162</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2627,25 +2627,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>442768</v>
+        <v>442902</v>
       </c>
       <c r="R20" t="n">
-        <v>7000121</v>
+        <v>7000213</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 23822-2024 artfynd.xlsx
+++ b/artfynd/A 23822-2024 artfynd.xlsx
@@ -1849,10 +1849,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800242</v>
+        <v>124800248</v>
       </c>
       <c r="B13" t="n">
-        <v>57635</v>
+        <v>91459</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1887,24 +1887,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442778</v>
+        <v>442739</v>
       </c>
       <c r="R13" t="n">
-        <v>7000153</v>
+        <v>7000176</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1963,7 +1955,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800238</v>
+        <v>124800242</v>
       </c>
       <c r="B14" t="n">
         <v>57635</v>
@@ -2015,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442812</v>
+        <v>442778</v>
       </c>
       <c r="R14" t="n">
-        <v>7000185</v>
+        <v>7000153</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,10 +2069,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800248</v>
+        <v>124800238</v>
       </c>
       <c r="B15" t="n">
-        <v>91459</v>
+        <v>57635</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2093,21 +2085,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2115,16 +2107,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fjälabodmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442739</v>
+        <v>442812</v>
       </c>
       <c r="R15" t="n">
-        <v>7000176</v>
+        <v>7000185</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 23822-2024 artfynd.xlsx
+++ b/artfynd/A 23822-2024 artfynd.xlsx
@@ -784,12 +784,7 @@
         <v>124800241</v>
       </c>
       <c r="B3" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1958,12 +1953,7 @@
         <v>124800242</v>
       </c>
       <c r="B14" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2072,12 +2062,7 @@
         <v>124800238</v>
       </c>
       <c r="B15" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2186,12 +2171,7 @@
         <v>124800240</v>
       </c>
       <c r="B16" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 23822-2024 artfynd.xlsx
+++ b/artfynd/A 23822-2024 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>124800241</v>
       </c>
       <c r="B3" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>124800242</v>
       </c>
       <c r="B14" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>124800238</v>
       </c>
       <c r="B15" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>124800240</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 23822-2024 artfynd.xlsx
+++ b/artfynd/A 23822-2024 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>124800241</v>
       </c>
       <c r="B3" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>124800242</v>
       </c>
       <c r="B14" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>124800238</v>
       </c>
       <c r="B15" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>124800240</v>
       </c>
       <c r="B16" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 23822-2024 artfynd.xlsx
+++ b/artfynd/A 23822-2024 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>124800241</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>124800242</v>
       </c>
       <c r="B14" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>124800238</v>
       </c>
       <c r="B15" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>124800240</v>
       </c>
       <c r="B16" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
